--- a/artfynd/A 45268-2022 artfynd.xlsx
+++ b/artfynd/A 45268-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120441749</v>
       </c>
       <c r="B2" t="n">
-        <v>95603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120441760</v>
+        <v>120441750</v>
       </c>
       <c r="B3" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492040</v>
+        <v>491972</v>
       </c>
       <c r="R3" t="n">
-        <v>6666768</v>
+        <v>6666882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,53 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120441925</v>
+        <v>120441921</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Aborrberg, Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491979</v>
+        <v>491960</v>
       </c>
       <c r="R4" t="n">
-        <v>6666893</v>
+        <v>6666776</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120441750</v>
+        <v>120441925</v>
       </c>
       <c r="B5" t="n">
-        <v>95603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aborrberg, Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491972</v>
+        <v>491979</v>
       </c>
       <c r="R5" t="n">
-        <v>6666882</v>
+        <v>6666893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,6 +1064,394 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120441760</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Aborrberg, Ludvika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492040</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6666768</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120441878</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Aborrberg, Ludvika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491961</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6666779</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120441856</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Aborrberg, Ludvika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>491952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6666809</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120441846</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Aborrberg, Ludvika, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>491961</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6666764</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
